--- a/tams-invest-parent/tams-invest-period/src/main/resources/tpl/TrdFundDuration001_ls.xlsx
+++ b/tams-invest-parent/tams-invest-period/src/main/resources/tpl/TrdFundDuration001_ls.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="110" windowWidth="14810" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>有效状态</t>
   </si>
@@ -27,50 +27,55 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>交易方向</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>权益登记日</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>除权日</t>
+  </si>
+  <si>
+    <t>分红到账日</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>红利再投日</t>
+  </si>
+  <si>
+    <t>权益登记日份额</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>单位分红净值</t>
+  </si>
+  <si>
+    <t>分红金额</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>分红份额</t>
+  </si>
+  <si>
+    <t>机构名称</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>分红类型</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>资产类型</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>资产简称</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>资产类型</t>
-  </si>
-  <si>
-    <t>分红类型</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>交易方向</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>权益登记日</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>除权日</t>
-  </si>
-  <si>
-    <t>分红到账日</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>红利再投日</t>
-  </si>
-  <si>
-    <t>权益登记日份额</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>单位分红净值</t>
-  </si>
-  <si>
-    <t>分红金额</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>分红份额</t>
-  </si>
-  <si>
-    <t>机构名称</t>
+    <t>合作资产</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -446,20 +451,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P3"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <dimension ref="A1:Q3"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="8.875" style="3" customWidth="1"/>
+    <col min="1" max="1" width="8.90625" style="3" customWidth="1"/>
     <col min="2" max="2" width="21" style="3" customWidth="1"/>
-    <col min="3" max="3" width="18" style="3" customWidth="1"/>
-    <col min="4" max="4" width="19.25" style="3" customWidth="1"/>
-    <col min="5" max="5" width="17.375" style="3" customWidth="1"/>
-    <col min="6" max="8" width="14.125" style="3" customWidth="1"/>
-    <col min="9" max="11" width="10.875" style="3" customWidth="1"/>
-    <col min="12" max="15" width="9" style="3"/>
+    <col min="3" max="5" width="18" style="3" customWidth="1"/>
+    <col min="6" max="9" width="14.08984375" style="3" customWidth="1"/>
+    <col min="10" max="12" width="10.90625" style="3" customWidth="1"/>
+    <col min="13" max="16" width="9" style="3"/>
+    <col min="18" max="18" width="4.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -470,46 +474,49 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="Q1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>15</v>
-      </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:17">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -525,9 +532,10 @@
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
-      <c r="P2" s="4"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="4"/>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:17">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -543,10 +551,12 @@
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
-      <c r="P3" s="4"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>